--- a/results_(stress_test)_PCCxSigmoid-PLI-/新建 Microsoft Excel 工作表.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLI-/新建 Microsoft Excel 工作表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_PCCxSigmoid-PLI-\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_PCCxSigmoid-PLI-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DDD27B-AE2C-4862-A9A3-A08558572166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A988F2DC-D86E-41D8-ACF5-BB3B3B25394D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -101,7 +106,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -394,40 +399,85 @@
       <c r="B2">
         <v>10</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2">
         <v>81.769470324137743</v>
+      </c>
+      <c r="D2" s="11">
+        <v>82.130949806370865</v>
+      </c>
+      <c r="E2" s="6">
+        <v>82.036173900004911</v>
+      </c>
+      <c r="F2" s="1">
+        <v>81.704048766281133</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>20</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3">
         <v>82.791431298425309</v>
+      </c>
+      <c r="D3" s="12">
+        <v>82.687289682436699</v>
+      </c>
+      <c r="E3" s="7">
+        <v>82.192201777985389</v>
+      </c>
+      <c r="F3" s="2">
+        <v>81.638886726240429</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>30</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4">
         <v>81.973286966150241</v>
+      </c>
+      <c r="D4" s="13">
+        <v>81.924140058881704</v>
+      </c>
+      <c r="E4" s="8">
+        <v>81.114159003682289</v>
+      </c>
+      <c r="F4" s="3">
+        <v>81.567853816497831</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>40</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5">
         <v>81.50374138184587</v>
+      </c>
+      <c r="D5" s="14">
+        <v>81.860734089395237</v>
+      </c>
+      <c r="E5" s="9">
+        <v>81.135880644872941</v>
+      </c>
+      <c r="F5" s="4">
+        <v>81.151422878513912</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>50</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6">
         <v>80.993673532354677</v>
+      </c>
+      <c r="D6" s="15">
+        <v>81.202441197588229</v>
+      </c>
+      <c r="E6" s="10">
+        <v>80.734942920498142</v>
+      </c>
+      <c r="F6" s="5">
+        <v>80.354492685922892</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -449,102 +499,87 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+      <c r="A10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+      <c r="A11" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11">
         <v>58.86245555757403</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6">
+      <c r="B12">
         <v>20</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12">
         <v>58.359406223237222</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6">
+      <c r="B13">
         <v>30</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13">
         <v>57.676257291729733</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6">
+      <c r="B14">
         <v>40</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14">
         <v>57.037113931204708</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6">
+      <c r="B15">
         <v>50</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15">
         <v>55.296631747102772</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6" t="s">
+      <c r="C16" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16">
         <v>200</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16">
         <v>100</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6" t="s">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C17" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C2:F6">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>